--- a/00_output/12_avoided_costs_ghg.xlsx
+++ b/00_output/12_avoided_costs_ghg.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>summer_gener._capacity_usdperKWH_carbon</t>
+          <t>summer_gener_capacity_usdperKWH_carbon</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>summer_gener._capacity_usdperKWH_n2o</t>
+          <t>summer_gener_capacity_usdperKWH_n2o</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>summer_gener._capacity_usdperKWH_ch4</t>
+          <t>summer_gener_capacity_usdperKWH_ch4</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
@@ -651,6 +651,56 @@
     <row r="11">
       <c r="A11" t="n">
         <v>2035</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2045</v>
       </c>
     </row>
   </sheetData>

--- a/00_output/12_avoided_costs_ghg.xlsx
+++ b/00_output/12_avoided_costs_ghg.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,31 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -42,12 +57,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,295 +458,1055 @@
   </sheetPr>
   <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="44" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="31" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="31" customWidth="1" min="17" max="17"/>
+    <col width="32" customWidth="1" min="18" max="18"/>
+    <col width="33" customWidth="1" min="19" max="19"/>
+    <col width="37" customWidth="1" min="20" max="20"/>
+    <col width="37" customWidth="1" min="21" max="21"/>
+    <col width="25" customWidth="1" min="22" max="22"/>
+    <col width="25" customWidth="1" min="23" max="23"/>
+    <col width="33" customWidth="1" min="24" max="24"/>
+    <col width="41" customWidth="1" min="25" max="25"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="31" customWidth="1" min="27" max="27"/>
+    <col width="30" customWidth="1" min="28" max="28"/>
+    <col width="31" customWidth="1" min="29" max="29"/>
+    <col width="32" customWidth="1" min="30" max="30"/>
+    <col width="33" customWidth="1" min="31" max="31"/>
+    <col width="37" customWidth="1" min="32" max="32"/>
+    <col width="37" customWidth="1" min="33" max="33"/>
+    <col width="25" customWidth="1" min="34" max="34"/>
+    <col width="25" customWidth="1" min="35" max="35"/>
+    <col width="33" customWidth="1" min="36" max="36"/>
+    <col width="41" customWidth="1" min="37" max="37"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>summer_on-peak_usdperKWH_carbon</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>summer_off-peak_usdperKWH_carbon</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>winter_on-peak_usdperKWH_carbon</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>winter_off-peak_usdperKWH_carbon</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>shoulder_on-peak_usdperKWH_carbon</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>shoulder_off-peak_usdperKWH_carbon</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>summer_gener_capacity_usdperKWH_carbon</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>winter_gener_capacity_usdperKWH_carbon</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>summer_td_usdperKWH_carbon</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>winter_td_usdperKWH_carbon</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>oil_residential_usdperMMBtu_carbon</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>natural_gas_residential_usdperMMBtu_carbon</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>summer_on-peak_usdperKWH_n2o</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>summer_off-peak_usdperKWH_n2o</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>winter_on-peak_usdperKWH_n2o</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>winter_off-peak_usdperKWH_n2o</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>shoulder_on-peak_usdperKWH_n2o</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>shoulder_off-peak_usdperKWH_n2o</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>summer_gener_capacity_usdperKWH_n2o</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>winter_gener_capacity_usdperKWH_n2o</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>summer_td_usdperKWH_n2o</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>winter_td_usdperKWH_n2o</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>oil_residential_usdperMMBtu_n2o</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>natural_gas_residential_usdperMMBtu_n2o</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>summer_on-peak_usdperKWH_ch4</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>summer_off-peak_usdperKWH_ch4</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>winter_on-peak_usdperKWH_ch4</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>winter_off-peak_usdperKWH_ch4</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>shoulder_on-peak_usdperKWH_ch4</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>shoulder_off-peak_usdperKWH_ch4</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>summer_gener_capacity_usdperKWH_ch4</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>winter_gener_capacity_usdperKWH_ch4</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>summer_td_usdperKWH_ch4</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>winter_td_usdperKWH_ch4</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>oil_residential_usdperMMBtu_ch4</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>natural_gas_residential_usdperMMBtu_ch4</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="2" t="n">
         <v>2026</v>
       </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="3" t="n"/>
+      <c r="O2" s="3" t="n"/>
+      <c r="P2" s="3" t="n"/>
+      <c r="Q2" s="3" t="n"/>
+      <c r="R2" s="3" t="n"/>
+      <c r="S2" s="3" t="n"/>
+      <c r="T2" s="3" t="n"/>
+      <c r="U2" s="3" t="n"/>
+      <c r="V2" s="3" t="n"/>
+      <c r="W2" s="3" t="n"/>
+      <c r="X2" s="3" t="n"/>
+      <c r="Y2" s="3" t="n"/>
+      <c r="Z2" s="3" t="n"/>
+      <c r="AA2" s="3" t="n"/>
+      <c r="AB2" s="3" t="n"/>
+      <c r="AC2" s="3" t="n"/>
+      <c r="AD2" s="3" t="n"/>
+      <c r="AE2" s="3" t="n"/>
+      <c r="AF2" s="3" t="n"/>
+      <c r="AG2" s="3" t="n"/>
+      <c r="AH2" s="3" t="n"/>
+      <c r="AI2" s="3" t="n"/>
+      <c r="AJ2" s="3" t="n"/>
+      <c r="AK2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="4" t="n">
         <v>2027</v>
       </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
+      <c r="Q3" s="5" t="n"/>
+      <c r="R3" s="5" t="n"/>
+      <c r="S3" s="5" t="n"/>
+      <c r="T3" s="5" t="n"/>
+      <c r="U3" s="5" t="n"/>
+      <c r="V3" s="5" t="n"/>
+      <c r="W3" s="5" t="n"/>
+      <c r="X3" s="5" t="n"/>
+      <c r="Y3" s="5" t="n"/>
+      <c r="Z3" s="5" t="n"/>
+      <c r="AA3" s="5" t="n"/>
+      <c r="AB3" s="5" t="n"/>
+      <c r="AC3" s="5" t="n"/>
+      <c r="AD3" s="5" t="n"/>
+      <c r="AE3" s="5" t="n"/>
+      <c r="AF3" s="5" t="n"/>
+      <c r="AG3" s="5" t="n"/>
+      <c r="AH3" s="5" t="n"/>
+      <c r="AI3" s="5" t="n"/>
+      <c r="AJ3" s="5" t="n"/>
+      <c r="AK3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="2" t="n">
         <v>2028</v>
       </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" s="3" t="n"/>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="n"/>
+      <c r="Z4" s="3" t="n"/>
+      <c r="AA4" s="3" t="n"/>
+      <c r="AB4" s="3" t="n"/>
+      <c r="AC4" s="3" t="n"/>
+      <c r="AD4" s="3" t="n"/>
+      <c r="AE4" s="3" t="n"/>
+      <c r="AF4" s="3" t="n"/>
+      <c r="AG4" s="3" t="n"/>
+      <c r="AH4" s="3" t="n"/>
+      <c r="AI4" s="3" t="n"/>
+      <c r="AJ4" s="3" t="n"/>
+      <c r="AK4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="4" t="n">
         <v>2029</v>
       </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+      <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="5" t="n"/>
+      <c r="AA5" s="5" t="n"/>
+      <c r="AB5" s="5" t="n"/>
+      <c r="AC5" s="5" t="n"/>
+      <c r="AD5" s="5" t="n"/>
+      <c r="AE5" s="5" t="n"/>
+      <c r="AF5" s="5" t="n"/>
+      <c r="AG5" s="5" t="n"/>
+      <c r="AH5" s="5" t="n"/>
+      <c r="AI5" s="5" t="n"/>
+      <c r="AJ5" s="5" t="n"/>
+      <c r="AK5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="2" t="n">
         <v>2030</v>
       </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3" t="n"/>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="3" t="n"/>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="3" t="n"/>
+      <c r="W6" s="3" t="n"/>
+      <c r="X6" s="3" t="n"/>
+      <c r="Y6" s="3" t="n"/>
+      <c r="Z6" s="3" t="n"/>
+      <c r="AA6" s="3" t="n"/>
+      <c r="AB6" s="3" t="n"/>
+      <c r="AC6" s="3" t="n"/>
+      <c r="AD6" s="3" t="n"/>
+      <c r="AE6" s="3" t="n"/>
+      <c r="AF6" s="3" t="n"/>
+      <c r="AG6" s="3" t="n"/>
+      <c r="AH6" s="3" t="n"/>
+      <c r="AI6" s="3" t="n"/>
+      <c r="AJ6" s="3" t="n"/>
+      <c r="AK6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="4" t="n">
         <v>2031</v>
       </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+      <c r="Y7" s="5" t="n"/>
+      <c r="Z7" s="5" t="n"/>
+      <c r="AA7" s="5" t="n"/>
+      <c r="AB7" s="5" t="n"/>
+      <c r="AC7" s="5" t="n"/>
+      <c r="AD7" s="5" t="n"/>
+      <c r="AE7" s="5" t="n"/>
+      <c r="AF7" s="5" t="n"/>
+      <c r="AG7" s="5" t="n"/>
+      <c r="AH7" s="5" t="n"/>
+      <c r="AI7" s="5" t="n"/>
+      <c r="AJ7" s="5" t="n"/>
+      <c r="AK7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="2" t="n">
         <v>2032</v>
       </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="n"/>
+      <c r="Q8" s="3" t="n"/>
+      <c r="R8" s="3" t="n"/>
+      <c r="S8" s="3" t="n"/>
+      <c r="T8" s="3" t="n"/>
+      <c r="U8" s="3" t="n"/>
+      <c r="V8" s="3" t="n"/>
+      <c r="W8" s="3" t="n"/>
+      <c r="X8" s="3" t="n"/>
+      <c r="Y8" s="3" t="n"/>
+      <c r="Z8" s="3" t="n"/>
+      <c r="AA8" s="3" t="n"/>
+      <c r="AB8" s="3" t="n"/>
+      <c r="AC8" s="3" t="n"/>
+      <c r="AD8" s="3" t="n"/>
+      <c r="AE8" s="3" t="n"/>
+      <c r="AF8" s="3" t="n"/>
+      <c r="AG8" s="3" t="n"/>
+      <c r="AH8" s="3" t="n"/>
+      <c r="AI8" s="3" t="n"/>
+      <c r="AJ8" s="3" t="n"/>
+      <c r="AK8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="4" t="n">
         <v>2033</v>
       </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
+      <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="5" t="n"/>
+      <c r="U9" s="5" t="n"/>
+      <c r="V9" s="5" t="n"/>
+      <c r="W9" s="5" t="n"/>
+      <c r="X9" s="5" t="n"/>
+      <c r="Y9" s="5" t="n"/>
+      <c r="Z9" s="5" t="n"/>
+      <c r="AA9" s="5" t="n"/>
+      <c r="AB9" s="5" t="n"/>
+      <c r="AC9" s="5" t="n"/>
+      <c r="AD9" s="5" t="n"/>
+      <c r="AE9" s="5" t="n"/>
+      <c r="AF9" s="5" t="n"/>
+      <c r="AG9" s="5" t="n"/>
+      <c r="AH9" s="5" t="n"/>
+      <c r="AI9" s="5" t="n"/>
+      <c r="AJ9" s="5" t="n"/>
+      <c r="AK9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="2" t="n">
         <v>2034</v>
       </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="n"/>
+      <c r="Q10" s="3" t="n"/>
+      <c r="R10" s="3" t="n"/>
+      <c r="S10" s="3" t="n"/>
+      <c r="T10" s="3" t="n"/>
+      <c r="U10" s="3" t="n"/>
+      <c r="V10" s="3" t="n"/>
+      <c r="W10" s="3" t="n"/>
+      <c r="X10" s="3" t="n"/>
+      <c r="Y10" s="3" t="n"/>
+      <c r="Z10" s="3" t="n"/>
+      <c r="AA10" s="3" t="n"/>
+      <c r="AB10" s="3" t="n"/>
+      <c r="AC10" s="3" t="n"/>
+      <c r="AD10" s="3" t="n"/>
+      <c r="AE10" s="3" t="n"/>
+      <c r="AF10" s="3" t="n"/>
+      <c r="AG10" s="3" t="n"/>
+      <c r="AH10" s="3" t="n"/>
+      <c r="AI10" s="3" t="n"/>
+      <c r="AJ10" s="3" t="n"/>
+      <c r="AK10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="4" t="n">
         <v>2035</v>
       </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
+      <c r="Q11" s="5" t="n"/>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" s="5" t="n"/>
+      <c r="T11" s="5" t="n"/>
+      <c r="U11" s="5" t="n"/>
+      <c r="V11" s="5" t="n"/>
+      <c r="W11" s="5" t="n"/>
+      <c r="X11" s="5" t="n"/>
+      <c r="Y11" s="5" t="n"/>
+      <c r="Z11" s="5" t="n"/>
+      <c r="AA11" s="5" t="n"/>
+      <c r="AB11" s="5" t="n"/>
+      <c r="AC11" s="5" t="n"/>
+      <c r="AD11" s="5" t="n"/>
+      <c r="AE11" s="5" t="n"/>
+      <c r="AF11" s="5" t="n"/>
+      <c r="AG11" s="5" t="n"/>
+      <c r="AH11" s="5" t="n"/>
+      <c r="AI11" s="5" t="n"/>
+      <c r="AJ11" s="5" t="n"/>
+      <c r="AK11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="2" t="n">
         <v>2036</v>
       </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="3" t="n"/>
+      <c r="Q12" s="3" t="n"/>
+      <c r="R12" s="3" t="n"/>
+      <c r="S12" s="3" t="n"/>
+      <c r="T12" s="3" t="n"/>
+      <c r="U12" s="3" t="n"/>
+      <c r="V12" s="3" t="n"/>
+      <c r="W12" s="3" t="n"/>
+      <c r="X12" s="3" t="n"/>
+      <c r="Y12" s="3" t="n"/>
+      <c r="Z12" s="3" t="n"/>
+      <c r="AA12" s="3" t="n"/>
+      <c r="AB12" s="3" t="n"/>
+      <c r="AC12" s="3" t="n"/>
+      <c r="AD12" s="3" t="n"/>
+      <c r="AE12" s="3" t="n"/>
+      <c r="AF12" s="3" t="n"/>
+      <c r="AG12" s="3" t="n"/>
+      <c r="AH12" s="3" t="n"/>
+      <c r="AI12" s="3" t="n"/>
+      <c r="AJ12" s="3" t="n"/>
+      <c r="AK12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="4" t="n">
         <v>2037</v>
       </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+      <c r="Q13" s="5" t="n"/>
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="5" t="n"/>
+      <c r="T13" s="5" t="n"/>
+      <c r="U13" s="5" t="n"/>
+      <c r="V13" s="5" t="n"/>
+      <c r="W13" s="5" t="n"/>
+      <c r="X13" s="5" t="n"/>
+      <c r="Y13" s="5" t="n"/>
+      <c r="Z13" s="5" t="n"/>
+      <c r="AA13" s="5" t="n"/>
+      <c r="AB13" s="5" t="n"/>
+      <c r="AC13" s="5" t="n"/>
+      <c r="AD13" s="5" t="n"/>
+      <c r="AE13" s="5" t="n"/>
+      <c r="AF13" s="5" t="n"/>
+      <c r="AG13" s="5" t="n"/>
+      <c r="AH13" s="5" t="n"/>
+      <c r="AI13" s="5" t="n"/>
+      <c r="AJ13" s="5" t="n"/>
+      <c r="AK13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="2" t="n">
         <v>2038</v>
       </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3" t="n"/>
+      <c r="O14" s="3" t="n"/>
+      <c r="P14" s="3" t="n"/>
+      <c r="Q14" s="3" t="n"/>
+      <c r="R14" s="3" t="n"/>
+      <c r="S14" s="3" t="n"/>
+      <c r="T14" s="3" t="n"/>
+      <c r="U14" s="3" t="n"/>
+      <c r="V14" s="3" t="n"/>
+      <c r="W14" s="3" t="n"/>
+      <c r="X14" s="3" t="n"/>
+      <c r="Y14" s="3" t="n"/>
+      <c r="Z14" s="3" t="n"/>
+      <c r="AA14" s="3" t="n"/>
+      <c r="AB14" s="3" t="n"/>
+      <c r="AC14" s="3" t="n"/>
+      <c r="AD14" s="3" t="n"/>
+      <c r="AE14" s="3" t="n"/>
+      <c r="AF14" s="3" t="n"/>
+      <c r="AG14" s="3" t="n"/>
+      <c r="AH14" s="3" t="n"/>
+      <c r="AI14" s="3" t="n"/>
+      <c r="AJ14" s="3" t="n"/>
+      <c r="AK14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="4" t="n">
         <v>2039</v>
       </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="5" t="n"/>
+      <c r="U15" s="5" t="n"/>
+      <c r="V15" s="5" t="n"/>
+      <c r="W15" s="5" t="n"/>
+      <c r="X15" s="5" t="n"/>
+      <c r="Y15" s="5" t="n"/>
+      <c r="Z15" s="5" t="n"/>
+      <c r="AA15" s="5" t="n"/>
+      <c r="AB15" s="5" t="n"/>
+      <c r="AC15" s="5" t="n"/>
+      <c r="AD15" s="5" t="n"/>
+      <c r="AE15" s="5" t="n"/>
+      <c r="AF15" s="5" t="n"/>
+      <c r="AG15" s="5" t="n"/>
+      <c r="AH15" s="5" t="n"/>
+      <c r="AI15" s="5" t="n"/>
+      <c r="AJ15" s="5" t="n"/>
+      <c r="AK15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="2" t="n">
         <v>2040</v>
       </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="3" t="n"/>
+      <c r="O16" s="3" t="n"/>
+      <c r="P16" s="3" t="n"/>
+      <c r="Q16" s="3" t="n"/>
+      <c r="R16" s="3" t="n"/>
+      <c r="S16" s="3" t="n"/>
+      <c r="T16" s="3" t="n"/>
+      <c r="U16" s="3" t="n"/>
+      <c r="V16" s="3" t="n"/>
+      <c r="W16" s="3" t="n"/>
+      <c r="X16" s="3" t="n"/>
+      <c r="Y16" s="3" t="n"/>
+      <c r="Z16" s="3" t="n"/>
+      <c r="AA16" s="3" t="n"/>
+      <c r="AB16" s="3" t="n"/>
+      <c r="AC16" s="3" t="n"/>
+      <c r="AD16" s="3" t="n"/>
+      <c r="AE16" s="3" t="n"/>
+      <c r="AF16" s="3" t="n"/>
+      <c r="AG16" s="3" t="n"/>
+      <c r="AH16" s="3" t="n"/>
+      <c r="AI16" s="3" t="n"/>
+      <c r="AJ16" s="3" t="n"/>
+      <c r="AK16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="4" t="n">
         <v>2041</v>
       </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
+      <c r="Q17" s="5" t="n"/>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" s="5" t="n"/>
+      <c r="T17" s="5" t="n"/>
+      <c r="U17" s="5" t="n"/>
+      <c r="V17" s="5" t="n"/>
+      <c r="W17" s="5" t="n"/>
+      <c r="X17" s="5" t="n"/>
+      <c r="Y17" s="5" t="n"/>
+      <c r="Z17" s="5" t="n"/>
+      <c r="AA17" s="5" t="n"/>
+      <c r="AB17" s="5" t="n"/>
+      <c r="AC17" s="5" t="n"/>
+      <c r="AD17" s="5" t="n"/>
+      <c r="AE17" s="5" t="n"/>
+      <c r="AF17" s="5" t="n"/>
+      <c r="AG17" s="5" t="n"/>
+      <c r="AH17" s="5" t="n"/>
+      <c r="AI17" s="5" t="n"/>
+      <c r="AJ17" s="5" t="n"/>
+      <c r="AK17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="2" t="n">
         <v>2042</v>
       </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
+      <c r="N18" s="3" t="n"/>
+      <c r="O18" s="3" t="n"/>
+      <c r="P18" s="3" t="n"/>
+      <c r="Q18" s="3" t="n"/>
+      <c r="R18" s="3" t="n"/>
+      <c r="S18" s="3" t="n"/>
+      <c r="T18" s="3" t="n"/>
+      <c r="U18" s="3" t="n"/>
+      <c r="V18" s="3" t="n"/>
+      <c r="W18" s="3" t="n"/>
+      <c r="X18" s="3" t="n"/>
+      <c r="Y18" s="3" t="n"/>
+      <c r="Z18" s="3" t="n"/>
+      <c r="AA18" s="3" t="n"/>
+      <c r="AB18" s="3" t="n"/>
+      <c r="AC18" s="3" t="n"/>
+      <c r="AD18" s="3" t="n"/>
+      <c r="AE18" s="3" t="n"/>
+      <c r="AF18" s="3" t="n"/>
+      <c r="AG18" s="3" t="n"/>
+      <c r="AH18" s="3" t="n"/>
+      <c r="AI18" s="3" t="n"/>
+      <c r="AJ18" s="3" t="n"/>
+      <c r="AK18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="4" t="n">
         <v>2043</v>
       </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
+      <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="5" t="n"/>
+      <c r="T19" s="5" t="n"/>
+      <c r="U19" s="5" t="n"/>
+      <c r="V19" s="5" t="n"/>
+      <c r="W19" s="5" t="n"/>
+      <c r="X19" s="5" t="n"/>
+      <c r="Y19" s="5" t="n"/>
+      <c r="Z19" s="5" t="n"/>
+      <c r="AA19" s="5" t="n"/>
+      <c r="AB19" s="5" t="n"/>
+      <c r="AC19" s="5" t="n"/>
+      <c r="AD19" s="5" t="n"/>
+      <c r="AE19" s="5" t="n"/>
+      <c r="AF19" s="5" t="n"/>
+      <c r="AG19" s="5" t="n"/>
+      <c r="AH19" s="5" t="n"/>
+      <c r="AI19" s="5" t="n"/>
+      <c r="AJ19" s="5" t="n"/>
+      <c r="AK19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="2" t="n">
         <v>2044</v>
       </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
+      <c r="N20" s="3" t="n"/>
+      <c r="O20" s="3" t="n"/>
+      <c r="P20" s="3" t="n"/>
+      <c r="Q20" s="3" t="n"/>
+      <c r="R20" s="3" t="n"/>
+      <c r="S20" s="3" t="n"/>
+      <c r="T20" s="3" t="n"/>
+      <c r="U20" s="3" t="n"/>
+      <c r="V20" s="3" t="n"/>
+      <c r="W20" s="3" t="n"/>
+      <c r="X20" s="3" t="n"/>
+      <c r="Y20" s="3" t="n"/>
+      <c r="Z20" s="3" t="n"/>
+      <c r="AA20" s="3" t="n"/>
+      <c r="AB20" s="3" t="n"/>
+      <c r="AC20" s="3" t="n"/>
+      <c r="AD20" s="3" t="n"/>
+      <c r="AE20" s="3" t="n"/>
+      <c r="AF20" s="3" t="n"/>
+      <c r="AG20" s="3" t="n"/>
+      <c r="AH20" s="3" t="n"/>
+      <c r="AI20" s="3" t="n"/>
+      <c r="AJ20" s="3" t="n"/>
+      <c r="AK20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="4" t="n">
         <v>2045</v>
       </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="5" t="n"/>
+      <c r="T21" s="5" t="n"/>
+      <c r="U21" s="5" t="n"/>
+      <c r="V21" s="5" t="n"/>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="5" t="n"/>
+      <c r="Y21" s="5" t="n"/>
+      <c r="Z21" s="5" t="n"/>
+      <c r="AA21" s="5" t="n"/>
+      <c r="AB21" s="5" t="n"/>
+      <c r="AC21" s="5" t="n"/>
+      <c r="AD21" s="5" t="n"/>
+      <c r="AE21" s="5" t="n"/>
+      <c r="AF21" s="5" t="n"/>
+      <c r="AG21" s="5" t="n"/>
+      <c r="AH21" s="5" t="n"/>
+      <c r="AI21" s="5" t="n"/>
+      <c r="AJ21" s="5" t="n"/>
+      <c r="AK21" s="5" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/00_output/12_avoided_costs_ghg.xlsx
+++ b/00_output/12_avoided_costs_ghg.xlsx
@@ -459,7 +459,7 @@
   <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
